--- a/backtest_runs/20260410_193731/by_symbol/SITC/SITC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SITC/SITC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>101500.2</v>
@@ -863,7 +863,7 @@
         <v>-276.8999999999994</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>104083.3</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>104083.3</v>
@@ -1001,7 +1001,7 @@
         <v>-1783.600000000004</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>106870.5</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>106870.5</v>
@@ -1093,7 +1093,7 @@
         <v>-634.3999999999994</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>106236.1</v>
@@ -1185,7 +1185,7 @@
         <v>-1089.399999999999</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>106879.6</v>
@@ -1231,7 +1231,7 @@
         <v>-15.60000000000059</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>106864</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>106864</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>106864</v>
@@ -1415,7 +1415,7 @@
         <v>-3317.599999999998</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>107663.5</v>
@@ -1507,7 +1507,7 @@
         <v>-40.29999999999291</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>109141.6</v>
@@ -1553,7 +1553,7 @@
         <v>-1684.800000000005</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>107456.8</v>
@@ -1645,7 +1645,7 @@
         <v>-4071.599999999992</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>110403.9</v>
